--- a/data/Ciclo de gente.xlsx
+++ b/data/Ciclo de gente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9324D5C4-460F-4792-8C7A-038FC7ACE289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D185E4-A41B-4C86-A574-F9657C0784A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
